--- a/data/trans_orig/IP07C10-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C10-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23388</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26404</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31681</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46839</t>
+          <t>46555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26952</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29937</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>45370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>29126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>19126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32713</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>27230</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>62,39%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>28132</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15829</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>26145</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>19800</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>40667</t>
+          <t>41049</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>57062</t>
+          <t>57490</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15121</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>43317</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>20778</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>18353</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>30733</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>38989</t>
+          <t>40488</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>57183</t>
+          <t>57115</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>32892</t>
+          <t>32624</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46304</t>
+          <t>46401</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27307</t>
+          <t>27517</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>40342</t>
+          <t>40296</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>63840</t>
+          <t>64056</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>83067</t>
+          <t>82427</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>95089</t>
+          <t>95716</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>121379</t>
+          <t>121488</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>104230</t>
+          <t>103230</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>130739</t>
+          <t>130986</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>205767</t>
+          <t>206096</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>245515</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>112991</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>139213</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>110160</t>
+          <t>109087</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>137218</t>
+          <t>137752</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>231285</t>
+          <t>228288</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>270919</t>
+          <t>267085</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>57987</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>71300</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>123115</t>
+          <t>123741</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>37628</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>40659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52843</t>
+          <t>52180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68495</t>
+          <t>68254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21769</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>35352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18602</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32598</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29493</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31698</t>
+          <t>30589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45403</t>
+          <t>45411</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25099</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22215</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20373</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>18773</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>36820</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>27299</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>38347</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>54670</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>25171</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29622</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>32317</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>51233</t>
+          <t>51683</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>45306</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>37964</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>51199</t>
+          <t>51688</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>71961</t>
+          <t>72752</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>92780</t>
+          <t>92548</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25691</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>92933</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>119529</t>
+          <t>119254</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>107728</t>
+          <t>107868</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>136017</t>
+          <t>136365</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>208698</t>
+          <t>208006</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>248685</t>
+          <t>246483</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>128681</t>
+          <t>129014</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>156157</t>
+          <t>156781</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>129166</t>
+          <t>129275</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>158250</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>266985</t>
+          <t>265068</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>306529</t>
+          <t>306428</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>32396</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>73664</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101649</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28231</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>23426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>26950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>38618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52979</t>
+          <t>54056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70760</t>
+          <t>70811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,37%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35370</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52778</t>
+          <t>51692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29488</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>43563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24846</t>
+          <t>25872</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24962</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46492</t>
+          <t>46892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>20911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>21607</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>31398</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>34140</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46355</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>35288</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>53743</t>
+          <t>53702</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34722</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>22598</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>35628</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>65492</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>29727</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>31686</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>57962</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>43042</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>32256</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>45604</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>64839</t>
+          <t>65291</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>85058</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>28811</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>123103</t>
+          <t>122974</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>155197</t>
+          <t>152817</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>125441</t>
+          <t>126821</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>155944</t>
+          <t>156022</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>259339</t>
+          <t>257749</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>303280</t>
+          <t>300514</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>127944</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>157467</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>134131</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>165913</t>
+          <t>164874</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>274137</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>313663</t>
+          <t>315800</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>38583</t>
+          <t>37989</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>107927</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
